--- a/scholarship_application_forms/023_open_education_resource_grant_application_form--scholarship_application_forms.xlsx
+++ b/scholarship_application_forms/023_open_education_resource_grant_application_form--scholarship_application_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'option_1',_'value':_'option-1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Option 1', 'value': 'option-1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'option_2',_'value':_'option-2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Option 2', 'value': 'option-2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'option_3',_'value':_'option-3'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Option 3', 'value': 'option-3'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'option_1.1',_'value':_'option-1-1'}</t>
+          <t>option_1.1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Option 1.1', 'value': 'option-1-1'}</t>
+          <t>Option 1.1</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'option_1.2',_'value':_'option-1-2'}</t>
+          <t>option_1.2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Option 1.2', 'value': 'option-1-2'}</t>
+          <t>Option 1.2</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'08:00',_'value':_'08:00'}</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': '08:00', 'value': '08:00'}</t>
+          <t>08:00</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'09:00',_'value':_'09:00'}</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': '09:00', 'value': '09:00'}</t>
+          <t>09:00</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_600,_'value':_600}</t>
+          <t>600</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 600, 'value': 600}</t>
+          <t>600</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_720,_'value':_720}</t>
+          <t>720</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 720, 'value': 720}</t>
+          <t>720</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_780,_'value':_780}</t>
+          <t>780</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 780, 'value': 780}</t>
+          <t>780</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_840,_'value':_840}</t>
+          <t>840</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 840, 'value': 840}</t>
+          <t>840</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_900,_'value':_900}</t>
+          <t>900</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 900, 'value': 900}</t>
+          <t>900</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_960,_'value':_960}</t>
+          <t>960</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 960, 'value': 960}</t>
+          <t>960</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_1020,_'value':_1020}</t>
+          <t>1020</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 1020, 'value': 1020}</t>
+          <t>1020</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'chat',_'value':_'chatjimmy'}</t>
+          <t>chat</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Chat', 'value': 'chatjimmy'}</t>
+          <t>Chat</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'jimmy',_'value':_'jimmy'}</t>
+          <t>jimmy</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Jimmy', 'value': 'jimmy'}</t>
+          <t>Jimmy</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'jimmy',_'value':_'jimmy'}</t>
+          <t>jimmy</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Jimmy', 'value': 'jimmy'}</t>
+          <t>Jimmy</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'chat',_'value':_'chatjimmy'}</t>
+          <t>chat</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Chat', 'value': 'chatjimmy'}</t>
+          <t>Chat</t>
         </is>
       </c>
     </row>
